--- a/artfynd/A 383-2026 artfynd.xlsx
+++ b/artfynd/A 383-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122383817</v>
+        <v>130794739</v>
       </c>
       <c r="B2" t="n">
-        <v>57264</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100011</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Finnfallet, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387552</v>
+        <v>387806</v>
       </c>
       <c r="R2" t="n">
-        <v>6627603</v>
+        <v>6627680</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>kungsörn cirklar sakta västerut på långt håll. tycker mig kunna se vit stjärtrot men inte helt säker.</t>
+          <t>Sparsamma förekomster. Inventering åt tekniska verken.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,15 +765,128 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122383817</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100011</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsörn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aquila chrysaetos</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Finnfallet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>387552</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6627603</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kungsörn cirklar sakta västerut på långt håll. tycker mig kunna se vit stjärtrot men inte helt säker.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Alessandra Munari</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Vesa Jussila</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
